--- a/data/trans_orig/P39A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39A-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2012 (tasa de respuesta: 96,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37387</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64825</t>
+          <t>65339</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62209</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76238</t>
+          <t>76722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114487</t>
+          <t>117389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85501</t>
+          <t>85068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123853</t>
+          <t>122188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>68971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105281</t>
+          <t>104101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165758</t>
+          <t>166721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217211</t>
+          <t>218062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123179</t>
+          <t>120261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164609</t>
+          <t>164154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77890</t>
+          <t>77911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>115416</t>
+          <t>115458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>209719</t>
+          <t>208618</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>265383</t>
+          <t>264025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>62287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97170</t>
+          <t>97850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70242</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105622</t>
+          <t>106332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>140517</t>
+          <t>142126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189781</t>
+          <t>189056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191495</t>
+          <t>187926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238493</t>
+          <t>235935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>259399</t>
+          <t>254104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308740</t>
+          <t>308306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462745</t>
+          <t>463584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>530611</t>
+          <t>533004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55434</t>
+          <t>56757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>91997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57253</t>
+          <t>56788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89391</t>
+          <t>89553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122926</t>
+          <t>121284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171865</t>
+          <t>168827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145647</t>
+          <t>143361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192708</t>
+          <t>191567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113650</t>
+          <t>111976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158541</t>
+          <t>158482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>271086</t>
+          <t>268424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334514</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179895</t>
+          <t>180220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228718</t>
+          <t>230868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183567</t>
+          <t>184880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237326</t>
+          <t>238999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>381722</t>
+          <t>378162</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>455091</t>
+          <t>450557</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>83112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120951</t>
+          <t>121574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104868</t>
+          <t>106760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147613</t>
+          <t>150460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200866</t>
+          <t>200377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261406</t>
+          <t>256367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230918</t>
+          <t>233700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287496</t>
+          <t>290332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>311100</t>
+          <t>306605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371833</t>
+          <t>368096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>555377</t>
+          <t>558518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>635431</t>
+          <t>640451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70573</t>
+          <t>69193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>64042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85451</t>
+          <t>85123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126889</t>
+          <t>126113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111240</t>
+          <t>112759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155061</t>
+          <t>154948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92192</t>
+          <t>91579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132682</t>
+          <t>133078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217395</t>
+          <t>214416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275833</t>
+          <t>275546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156788</t>
+          <t>157037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>206609</t>
+          <t>204836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>141455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>189970</t>
+          <t>189511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>311180</t>
+          <t>313324</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>378178</t>
+          <t>379370</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48074</t>
+          <t>48562</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>81202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83953</t>
+          <t>84893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124076</t>
+          <t>122330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142347</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191113</t>
+          <t>191270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156300</t>
+          <t>155700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204763</t>
+          <t>204855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219481</t>
+          <t>219633</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269775</t>
+          <t>271623</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>387463</t>
+          <t>392924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461938</t>
+          <t>465892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56150</t>
+          <t>57607</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90101</t>
+          <t>89569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64029</t>
+          <t>64605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98647</t>
+          <t>101020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129659</t>
+          <t>128884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178048</t>
+          <t>176719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>159959</t>
+          <t>163081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208037</t>
+          <t>208991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148657</t>
+          <t>149666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196803</t>
+          <t>196312</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>318726</t>
+          <t>318877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>388146</t>
+          <t>388177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132931</t>
+          <t>132035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>179838</t>
+          <t>180469</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>163392</t>
+          <t>159799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210668</t>
+          <t>210087</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>307082</t>
+          <t>311329</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375994</t>
+          <t>376498</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77925</t>
+          <t>78215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117886</t>
+          <t>117211</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86943</t>
+          <t>88532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126194</t>
+          <t>127370</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175220</t>
+          <t>174563</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228131</t>
+          <t>229150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>242578</t>
+          <t>241757</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>299841</t>
+          <t>298432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>357090</t>
+          <t>354792</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>416235</t>
+          <t>414338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>616853</t>
+          <t>616860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>695096</t>
+          <t>698028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>217512</t>
+          <t>214990</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>280180</t>
+          <t>278637</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>216713</t>
+          <t>216487</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>278240</t>
+          <t>280465</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>448323</t>
+          <t>451979</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>537900</t>
+          <t>544991</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>543143</t>
+          <t>549014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>629683</t>
+          <t>635409</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>462062</t>
+          <t>457746</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>544655</t>
+          <t>542231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1033279</t>
+          <t>1033802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1159767</t>
+          <t>1150622</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>635972</t>
+          <t>635365</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>733696</t>
+          <t>729913</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>608555</t>
+          <t>612886</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>705354</t>
+          <t>705024</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1278395</t>
+          <t>1281495</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1402760</t>
+          <t>1408234</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>300581</t>
+          <t>299785</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>374841</t>
+          <t>372835</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>383257</t>
+          <t>382887</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>461118</t>
+          <t>463981</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>702794</t>
+          <t>705143</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>819541</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>876683</t>
+          <t>871601</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>981059</t>
+          <t>974694</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1192521</t>
+          <t>1197630</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1307740</t>
+          <t>1311213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2104087</t>
+          <t>2098365</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2249157</t>
+          <t>2254039</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2016 (tasa de respuesta: 96,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52684</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84180</t>
+          <t>82812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>38059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65052</t>
+          <t>66603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98811</t>
+          <t>99116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142845</t>
+          <t>140671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108165</t>
+          <t>109920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148984</t>
+          <t>147980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109978</t>
+          <t>109119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148769</t>
+          <t>149698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228176</t>
+          <t>230148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287413</t>
+          <t>284614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>137966</t>
+          <t>135972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179593</t>
+          <t>177710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126874</t>
+          <t>126499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169664</t>
+          <t>170559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>273485</t>
+          <t>276883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>335432</t>
+          <t>335101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61824</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96590</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69204</t>
+          <t>68619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104350</t>
+          <t>102375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137661</t>
+          <t>139872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187570</t>
+          <t>184493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100767</t>
+          <t>99944</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139282</t>
+          <t>139669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141946</t>
+          <t>142611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185737</t>
+          <t>184231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254737</t>
+          <t>249866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314562</t>
+          <t>311220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>95141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137916</t>
+          <t>135200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96489</t>
+          <t>97042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137867</t>
+          <t>137186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206938</t>
+          <t>203963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261299</t>
+          <t>263334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>179397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229735</t>
+          <t>229180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212498</t>
+          <t>209626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>265909</t>
+          <t>266934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403973</t>
+          <t>403169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480022</t>
+          <t>477509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197470</t>
+          <t>199182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>250070</t>
+          <t>251065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200620</t>
+          <t>200578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>256738</t>
+          <t>254384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414320</t>
+          <t>414323</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>487544</t>
+          <t>486614</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87789</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127016</t>
+          <t>125276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125274</t>
+          <t>123939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170285</t>
+          <t>172531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223714</t>
+          <t>221929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284315</t>
+          <t>282272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147725</t>
+          <t>149279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197273</t>
+          <t>199013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179287</t>
+          <t>179237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230465</t>
+          <t>234276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341127</t>
+          <t>340286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410577</t>
+          <t>411209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>46083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75802</t>
+          <t>76663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39375</t>
+          <t>39347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>66582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89106</t>
+          <t>91131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133054</t>
+          <t>134037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164226</t>
+          <t>165045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212638</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159388</t>
+          <t>158244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206908</t>
+          <t>204785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337247</t>
+          <t>333886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404955</t>
+          <t>402949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150494</t>
+          <t>150939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>195730</t>
+          <t>195757</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192047</t>
+          <t>190422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>238799</t>
+          <t>239965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356104</t>
+          <t>355649</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>420947</t>
+          <t>423791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53581</t>
+          <t>54330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85430</t>
+          <t>86204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68685</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103722</t>
+          <t>100730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128144</t>
+          <t>128212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175058</t>
+          <t>174926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94165</t>
+          <t>92208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130423</t>
+          <t>132055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138877</t>
+          <t>141950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184231</t>
+          <t>185934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245403</t>
+          <t>241746</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305863</t>
+          <t>304495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71623</t>
+          <t>72828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106497</t>
+          <t>106713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>49165</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80036</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127952</t>
+          <t>130501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174650</t>
+          <t>175486</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168361</t>
+          <t>166660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216958</t>
+          <t>215221</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>178573</t>
+          <t>180979</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>229085</t>
+          <t>231464</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>363091</t>
+          <t>360619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>432846</t>
+          <t>431606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174464</t>
+          <t>174846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>223067</t>
+          <t>222882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204421</t>
+          <t>203457</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>254879</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>392184</t>
+          <t>394783</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>466354</t>
+          <t>465853</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95787</t>
+          <t>94869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134847</t>
+          <t>132490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121652</t>
+          <t>121602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168623</t>
+          <t>168133</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226491</t>
+          <t>226969</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>290746</t>
+          <t>288680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143359</t>
+          <t>145646</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189831</t>
+          <t>191588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>211026</t>
+          <t>210320</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>265008</t>
+          <t>264622</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>368052</t>
+          <t>365001</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>440439</t>
+          <t>439699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>296743</t>
+          <t>294100</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>367328</t>
+          <t>364665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>251211</t>
+          <t>249456</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316111</t>
+          <t>319216</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>562479</t>
+          <t>567601</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>659638</t>
+          <t>664337</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>666737</t>
+          <t>662924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>761297</t>
+          <t>758109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>707656</t>
+          <t>708765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>803032</t>
+          <t>800290</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395484</t>
+          <t>1396210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1522952</t>
+          <t>1530446</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>707762</t>
+          <t>709811</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>801663</t>
+          <t>802526</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>766533</t>
+          <t>769554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>869970</t>
+          <t>869745</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1504974</t>
+          <t>1506284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1649142</t>
+          <t>1646892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>330128</t>
+          <t>326277</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>404115</t>
+          <t>401820</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>422528</t>
+          <t>420013</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>499896</t>
+          <t>500348</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>769767</t>
+          <t>772443</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>876978</t>
+          <t>884248</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>519855</t>
+          <t>522347</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>605924</t>
+          <t>610855</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>712678</t>
+          <t>718020</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>812101</t>
+          <t>819704</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1267278</t>
+          <t>1269267</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1395925</t>
+          <t>1398720</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2023 (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72047</t>
+          <t>70932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72062</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90500</t>
+          <t>93471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133748</t>
+          <t>134801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120392</t>
+          <t>120523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168977</t>
+          <t>168778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104299</t>
+          <t>104839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136427</t>
+          <t>136693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235051</t>
+          <t>234073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295313</t>
+          <t>291193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122279</t>
+          <t>122818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163017</t>
+          <t>161268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>133911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165740</t>
+          <t>165664</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>262560</t>
+          <t>265870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>314972</t>
+          <t>318573</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>86609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>125216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106381</t>
+          <t>106889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136611</t>
+          <t>137586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201677</t>
+          <t>198020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249289</t>
+          <t>247625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106699</t>
+          <t>108666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>145131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155614</t>
+          <t>155946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189551</t>
+          <t>189874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>268475</t>
+          <t>272068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322267</t>
+          <t>320728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54006</t>
+          <t>54778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90359</t>
+          <t>89377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>47869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74203</t>
+          <t>74691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111732</t>
+          <t>109543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156233</t>
+          <t>153746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146822</t>
+          <t>144456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200997</t>
+          <t>199230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162575</t>
+          <t>164225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>203758</t>
+          <t>207340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321133</t>
+          <t>324978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>390081</t>
+          <t>388308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218402</t>
+          <t>217392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279145</t>
+          <t>274499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>215033</t>
+          <t>213050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257605</t>
+          <t>255037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>446199</t>
+          <t>448862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>522377</t>
+          <t>523231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105139</t>
+          <t>106082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>147667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130894</t>
+          <t>129041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164801</t>
+          <t>165184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244994</t>
+          <t>243548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302902</t>
+          <t>299417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132972</t>
+          <t>133876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177176</t>
+          <t>178997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196487</t>
+          <t>196994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242402</t>
+          <t>242019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342982</t>
+          <t>341593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404792</t>
+          <t>402149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67712</t>
+          <t>69903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80677</t>
+          <t>80989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63689</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138427</t>
+          <t>136942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167160</t>
+          <t>167749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219700</t>
+          <t>219012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231779</t>
+          <t>234032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>652228</t>
+          <t>624907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425809</t>
+          <t>424878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>894770</t>
+          <t>930357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>132139</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176567</t>
+          <t>179715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95930</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>301959</t>
+          <t>303963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231179</t>
+          <t>231418</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>455234</t>
+          <t>453477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73431</t>
+          <t>73838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>110719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>114349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107518</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>216151</t>
+          <t>212872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81622</t>
+          <t>84211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120783</t>
+          <t>122585</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49555</t>
+          <t>55983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162478</t>
+          <t>161743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122851</t>
+          <t>127948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263812</t>
+          <t>264698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40900</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>68906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53613</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81955</t>
+          <t>79604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99879</t>
+          <t>100493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142587</t>
+          <t>139638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>149052</t>
+          <t>148419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197818</t>
+          <t>197701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149615</t>
+          <t>151370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>190206</t>
+          <t>188905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>311020</t>
+          <t>308732</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>371380</t>
+          <t>377281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>188921</t>
+          <t>193319</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240029</t>
+          <t>243078</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>223635</t>
+          <t>223782</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>267635</t>
+          <t>267721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>427189</t>
+          <t>427000</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>495714</t>
+          <t>495097</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113574</t>
+          <t>112580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155065</t>
+          <t>153556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>134109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169689</t>
+          <t>169676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>257971</t>
+          <t>258833</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314587</t>
+          <t>313624</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>148963</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188950</t>
+          <t>191107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>227728</t>
+          <t>226978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>272310</t>
+          <t>274643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>383813</t>
+          <t>385583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>448500</t>
+          <t>452174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193895</t>
+          <t>193576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>260232</t>
+          <t>261070</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190033</t>
+          <t>195011</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>272196</t>
+          <t>273208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>412905</t>
+          <t>406690</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>517933</t>
+          <t>513642</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>625455</t>
+          <t>625343</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>726293</t>
+          <t>726421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>694737</t>
+          <t>690072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1405930</t>
+          <t>1289495</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1365854</t>
+          <t>1361363</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2206118</t>
+          <t>2064760</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>708065</t>
+          <t>708663</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>809128</t>
+          <t>815224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>653804</t>
+          <t>685357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>924241</t>
+          <t>935607</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1394437</t>
+          <t>1414719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1695853</t>
+          <t>1695985</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>414888</t>
+          <t>415050</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>491504</t>
+          <t>493998</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>398493</t>
+          <t>404168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>551430</t>
+          <t>552432</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>840732</t>
+          <t>842092</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1019229</t>
+          <t>1012934</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>509595</t>
+          <t>507085</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>592861</t>
+          <t>591547</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>592146</t>
+          <t>613698</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>825232</t>
+          <t>826403</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1126352</t>
+          <t>1158827</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1376580</t>
+          <t>1380547</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39A-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65339</t>
+          <t>65287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>62730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76722</t>
+          <t>76063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>116125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85068</t>
+          <t>86735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122188</t>
+          <t>125479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,47 +860,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>86838</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69725</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105286</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>14,5%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86838</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68971</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>104101</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166721</t>
+          <t>165939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218062</t>
+          <t>219076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120261</t>
+          <t>121320</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164154</t>
+          <t>162833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>78417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>115458</t>
+          <t>114578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>208618</t>
+          <t>209668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>264025</t>
+          <t>268369</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>62568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97850</t>
+          <t>97366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70993</t>
+          <t>71917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106332</t>
+          <t>106051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142126</t>
+          <t>139592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189056</t>
+          <t>189500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187926</t>
+          <t>191708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>235935</t>
+          <t>238434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254104</t>
+          <t>260958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308306</t>
+          <t>308522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463584</t>
+          <t>463019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>533004</t>
+          <t>534490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56757</t>
+          <t>56947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91997</t>
+          <t>91535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>56935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89553</t>
+          <t>89150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121284</t>
+          <t>121637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168827</t>
+          <t>168261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143361</t>
+          <t>144995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191567</t>
+          <t>192562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111976</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158482</t>
+          <t>158074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268424</t>
+          <t>271030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332508</t>
+          <t>333210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180220</t>
+          <t>179710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>230868</t>
+          <t>230928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184880</t>
+          <t>185549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>238999</t>
+          <t>237037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>378162</t>
+          <t>381220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>450557</t>
+          <t>455370</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83112</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121574</t>
+          <t>123051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200377</t>
+          <t>200079</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256367</t>
+          <t>259501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233700</t>
+          <t>233373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290332</t>
+          <t>291913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>306605</t>
+          <t>307619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368096</t>
+          <t>367017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558518</t>
+          <t>559724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>640451</t>
+          <t>642272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>69190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>37064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64042</t>
+          <t>65560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>81900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126113</t>
+          <t>125453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112759</t>
+          <t>113605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154948</t>
+          <t>158184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91579</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133078</t>
+          <t>130682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214416</t>
+          <t>220020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275546</t>
+          <t>277675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157037</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>204836</t>
+          <t>206468</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>141455</t>
+          <t>142818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>189511</t>
+          <t>188447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>313324</t>
+          <t>313877</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>379370</t>
+          <t>379069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48562</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81202</t>
+          <t>80873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84893</t>
+          <t>84226</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122330</t>
+          <t>123785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142395</t>
+          <t>141956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191270</t>
+          <t>190721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155700</t>
+          <t>156604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204855</t>
+          <t>202171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219633</t>
+          <t>219782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271623</t>
+          <t>271058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>392924</t>
+          <t>388687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>465892</t>
+          <t>458155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57607</t>
+          <t>58063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89569</t>
+          <t>90117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>64376</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101020</t>
+          <t>101369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128884</t>
+          <t>128057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176719</t>
+          <t>178572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163081</t>
+          <t>161652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208991</t>
+          <t>208616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149666</t>
+          <t>148497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196312</t>
+          <t>196791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>318877</t>
+          <t>321675</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>388177</t>
+          <t>392105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132035</t>
+          <t>132860</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180469</t>
+          <t>181013</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>159799</t>
+          <t>160718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210087</t>
+          <t>213734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>311329</t>
+          <t>308856</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>376498</t>
+          <t>377666</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78215</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117211</t>
+          <t>117731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127370</t>
+          <t>125766</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174563</t>
+          <t>175263</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229150</t>
+          <t>233027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>241757</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>298432</t>
+          <t>300990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>354792</t>
+          <t>356471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>414338</t>
+          <t>415909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>616860</t>
+          <t>612280</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>698028</t>
+          <t>697376</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>214990</t>
+          <t>217469</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>278637</t>
+          <t>280771</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>216487</t>
+          <t>220587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>280465</t>
+          <t>281037</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>451979</t>
+          <t>445950</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>544991</t>
+          <t>540367</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>549014</t>
+          <t>549046</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>635409</t>
+          <t>637726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>457746</t>
+          <t>460790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>542231</t>
+          <t>544093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1033802</t>
+          <t>1033850</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1150622</t>
+          <t>1153371</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>635365</t>
+          <t>637138</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>729913</t>
+          <t>725093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,82 +3701,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>26,06%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>657479</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>610783</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>703747</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>19,81%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1339803</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>1275342</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>1408986</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>22,84%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>657479</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>612886</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>705024</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1339803</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1281495</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1408234</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>299785</t>
+          <t>301149</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>372835</t>
+          <t>374541</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>382887</t>
+          <t>385931</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>463981</t>
+          <t>464650</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>705143</t>
+          <t>704050</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>810662</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>871601</t>
+          <t>874230</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>974694</t>
+          <t>979158</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1197630</t>
+          <t>1197127</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1311213</t>
+          <t>1314139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2098365</t>
+          <t>2105213</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2254039</t>
+          <t>2251505</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>52847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82812</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66603</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99116</t>
+          <t>97733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140671</t>
+          <t>140172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>109411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147980</t>
+          <t>147220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109119</t>
+          <t>111534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>149358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230148</t>
+          <t>229907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284614</t>
+          <t>287093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135972</t>
+          <t>137077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177710</t>
+          <t>179613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126499</t>
+          <t>127377</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170559</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>276883</t>
+          <t>277934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>335101</t>
+          <t>336185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>62741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68619</t>
+          <t>69887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>102267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139872</t>
+          <t>139469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184493</t>
+          <t>188016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99944</t>
+          <t>100423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139669</t>
+          <t>139497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142611</t>
+          <t>140420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184231</t>
+          <t>184290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>249866</t>
+          <t>253739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>311220</t>
+          <t>315397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95141</t>
+          <t>94248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135200</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97042</t>
+          <t>96787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137186</t>
+          <t>138228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203963</t>
+          <t>198167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>263334</t>
+          <t>260849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179397</t>
+          <t>178593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229180</t>
+          <t>229101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>209626</t>
+          <t>211100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266934</t>
+          <t>268016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403169</t>
+          <t>403387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>477509</t>
+          <t>477766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>199182</t>
+          <t>195921</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>251065</t>
+          <t>248677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200578</t>
+          <t>201801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>253593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414323</t>
+          <t>413320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>486614</t>
+          <t>486371</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125276</t>
+          <t>123891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123939</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172531</t>
+          <t>173746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221929</t>
+          <t>221248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282272</t>
+          <t>281169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149279</t>
+          <t>146456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199013</t>
+          <t>194573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179237</t>
+          <t>179388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234276</t>
+          <t>230539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340286</t>
+          <t>341656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411209</t>
+          <t>410736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>44024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76663</t>
+          <t>76373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66582</t>
+          <t>67156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>90752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134037</t>
+          <t>133229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165045</t>
+          <t>163620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>211324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158244</t>
+          <t>155933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204785</t>
+          <t>205597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>333886</t>
+          <t>337758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402949</t>
+          <t>402766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150939</t>
+          <t>153155</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>195757</t>
+          <t>200037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190422</t>
+          <t>190910</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>239965</t>
+          <t>240758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>355649</t>
+          <t>356954</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>423791</t>
+          <t>423628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54330</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86204</t>
+          <t>86737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>67182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100730</t>
+          <t>102820</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128212</t>
+          <t>128772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174926</t>
+          <t>175746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92208</t>
+          <t>91851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132055</t>
+          <t>135464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141950</t>
+          <t>141098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185934</t>
+          <t>186212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241746</t>
+          <t>242426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>304495</t>
+          <t>303832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72828</t>
+          <t>72021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106713</t>
+          <t>106385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80871</t>
+          <t>79983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130501</t>
+          <t>128814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175486</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166660</t>
+          <t>167989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215221</t>
+          <t>219207</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180979</t>
+          <t>177689</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>231464</t>
+          <t>228835</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>360619</t>
+          <t>361205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>431606</t>
+          <t>431390</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174846</t>
+          <t>173626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>222882</t>
+          <t>221954</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>203457</t>
+          <t>204041</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>254879</t>
+          <t>255972</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>394783</t>
+          <t>392897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>465853</t>
+          <t>463170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94869</t>
+          <t>95239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132490</t>
+          <t>134943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121602</t>
+          <t>119826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168133</t>
+          <t>166378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226969</t>
+          <t>229517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>288680</t>
+          <t>291057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145646</t>
+          <t>140982</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191588</t>
+          <t>189055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>210320</t>
+          <t>210717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>264622</t>
+          <t>264961</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>365001</t>
+          <t>368800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>439699</t>
+          <t>443931</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>294100</t>
+          <t>293751</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>364665</t>
+          <t>364256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>249456</t>
+          <t>252393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>319216</t>
+          <t>313395</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>567601</t>
+          <t>565214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>664337</t>
+          <t>661610</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>662924</t>
+          <t>656765</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>758109</t>
+          <t>754963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>708765</t>
+          <t>712037</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>800290</t>
+          <t>810710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396210</t>
+          <t>1392870</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1530446</t>
+          <t>1526191</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>709811</t>
+          <t>705498</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>802526</t>
+          <t>799559</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>769554</t>
+          <t>774239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>869745</t>
+          <t>876242</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1506284</t>
+          <t>1506462</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1646892</t>
+          <t>1649248</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>326277</t>
+          <t>323621</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>401820</t>
+          <t>397811</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>420013</t>
+          <t>416323</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>500348</t>
+          <t>498369</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>772443</t>
+          <t>767521</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>884248</t>
+          <t>873804</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>522347</t>
+          <t>524252</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>610855</t>
+          <t>609915</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>718020</t>
+          <t>718102</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>819704</t>
+          <t>818604</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1269267</t>
+          <t>1267735</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1398720</t>
+          <t>1399287</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51420</t>
+          <t>58344</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>42095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70932</t>
+          <t>77520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>62521</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>51631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72169</t>
+          <t>77409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>110180</t>
+          <t>120865</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93471</t>
+          <t>102938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134801</t>
+          <t>144947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>142042</t>
+          <t>144315</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120523</t>
+          <t>121424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168778</t>
+          <t>167361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120111</t>
+          <t>127132</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104839</t>
+          <t>110359</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136693</t>
+          <t>142619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>262153</t>
+          <t>271448</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234073</t>
+          <t>245321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291193</t>
+          <t>303437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>141388</t>
+          <t>155684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122818</t>
+          <t>135813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161268</t>
+          <t>179210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>164275</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133911</t>
+          <t>146273</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165664</t>
+          <t>181656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>290717</t>
+          <t>319959</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>265870</t>
+          <t>292612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>318573</t>
+          <t>345705</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>103902</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86609</t>
+          <t>95638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125216</t>
+          <t>133605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>120320</t>
+          <t>129592</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106889</t>
+          <t>112895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137586</t>
+          <t>146699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>224221</t>
+          <t>243893</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198020</t>
+          <t>218995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247625</t>
+          <t>270069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>125589</t>
+          <t>135979</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108666</t>
+          <t>116734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145131</t>
+          <t>156292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>171700</t>
+          <t>182668</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155946</t>
+          <t>165095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189874</t>
+          <t>202325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>297289</t>
+          <t>318647</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272068</t>
+          <t>290769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320728</t>
+          <t>347816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>564340</t>
+          <t>608623</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>564340</t>
+          <t>608623</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>564340</t>
+          <t>608623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>620221</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>620221</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>620221</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1184561</t>
+          <t>1274811</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1184561</t>
+          <t>1274811</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1184561</t>
+          <t>1274811</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,27 +8693,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70853</t>
+          <t>77420</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54778</t>
+          <t>60514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89377</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59901</t>
+          <t>67170</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>53757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>82425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>130754</t>
+          <t>144590</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109543</t>
+          <t>123282</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153746</t>
+          <t>168821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>171816</t>
+          <t>188587</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144456</t>
+          <t>163358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199230</t>
+          <t>218746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>183125</t>
+          <t>202131</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164225</t>
+          <t>180670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207340</t>
+          <t>224915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>354941</t>
+          <t>390718</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324978</t>
+          <t>357645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>388308</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>247121</t>
+          <t>265629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217392</t>
+          <t>236144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274499</t>
+          <t>299917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>234966</t>
+          <t>263589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213050</t>
+          <t>241736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>255037</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>482087</t>
+          <t>529218</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>448862</t>
+          <t>495260</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>523231</t>
+          <t>566573</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126192</t>
+          <t>138651</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106082</t>
+          <t>117727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147667</t>
+          <t>162278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,67 +9067,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>146942</t>
+          <t>162539</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129041</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165184</t>
+          <t>183646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>301190</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>271731</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>330550</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>15,29%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>273134</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>243548</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>299417</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>152833</t>
+          <t>171588</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133876</t>
+          <t>148221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178997</t>
+          <t>198202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>219089</t>
+          <t>239928</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196994</t>
+          <t>217105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242019</t>
+          <t>263472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>371922</t>
+          <t>411516</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341593</t>
+          <t>382674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402149</t>
+          <t>453725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>768815</t>
+          <t>841875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>768815</t>
+          <t>841875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>768815</t>
+          <t>841875</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>844023</t>
+          <t>935357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>844023</t>
+          <t>935357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>844023</t>
+          <t>935357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1612838</t>
+          <t>1777231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1612838</t>
+          <t>1777231</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1612838</t>
+          <t>1777231</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49163</t>
+          <t>55774</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34590</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69903</t>
+          <t>75302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>56125</t>
+          <t>61169</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80989</t>
+          <t>75571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>116943</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>97386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136942</t>
+          <t>140615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>191570</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167749</t>
+          <t>193940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219012</t>
+          <t>246362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>391177</t>
+          <t>214413</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234032</t>
+          <t>190517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>624907</t>
+          <t>237051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>582748</t>
+          <t>433204</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424878</t>
+          <t>399466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>930357</t>
+          <t>468915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153865</t>
+          <t>170526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132139</t>
+          <t>144459</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179715</t>
+          <t>195145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212519</t>
+          <t>206834</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110784</t>
+          <t>185980</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>303963</t>
+          <t>231098</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>366384</t>
+          <t>377360</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231418</t>
+          <t>343214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>453477</t>
+          <t>410553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90937</t>
+          <t>102662</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73838</t>
+          <t>82488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110719</t>
+          <t>122955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>82139</t>
+          <t>100348</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38822</t>
+          <t>85889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114349</t>
+          <t>118400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>173076</t>
+          <t>203010</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96913</t>
+          <t>177404</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>229180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>100988</t>
+          <t>115809</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84211</t>
+          <t>97163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122585</t>
+          <t>139897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>116190</t>
+          <t>144987</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55983</t>
+          <t>126806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>161743</t>
+          <t>166846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>217178</t>
+          <t>260796</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127948</t>
+          <t>234758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264698</t>
+          <t>289744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>586523</t>
+          <t>663562</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>586523</t>
+          <t>663562</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>586523</t>
+          <t>663562</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>858150</t>
+          <t>727751</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>858150</t>
+          <t>727751</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>858150</t>
+          <t>727751</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1444674</t>
+          <t>1391313</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1444674</t>
+          <t>1391313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1444674</t>
+          <t>1391313</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53353</t>
+          <t>58761</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39822</t>
+          <t>43754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68906</t>
+          <t>75761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66053</t>
+          <t>68414</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53144</t>
+          <t>55849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79604</t>
+          <t>84662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>119406</t>
+          <t>127175</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100493</t>
+          <t>105924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139638</t>
+          <t>148627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>171257</t>
+          <t>186244</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148419</t>
+          <t>162565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197701</t>
+          <t>211715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>169580</t>
+          <t>186202</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>151370</t>
+          <t>165882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188905</t>
+          <t>209047</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>340837</t>
+          <t>372446</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308732</t>
+          <t>336368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>377281</t>
+          <t>406291</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>215088</t>
+          <t>220412</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193319</t>
+          <t>196786</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>249090</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>245303</t>
+          <t>264587</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>223782</t>
+          <t>240698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>267721</t>
+          <t>288031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>460391</t>
+          <t>484999</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>427000</t>
+          <t>452587</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>495097</t>
+          <t>520338</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>132314</t>
+          <t>138526</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112580</t>
+          <t>119911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153556</t>
+          <t>161357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,67 +10431,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>151559</t>
+          <t>161431</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134109</t>
+          <t>142661</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169676</t>
+          <t>182139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>299957</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>273509</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>331667</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>19,24%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>283872</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>258833</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>313624</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>167724</t>
+          <t>171808</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148963</t>
+          <t>150335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191107</t>
+          <t>196318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>249347</t>
+          <t>267114</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>226978</t>
+          <t>242458</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>274643</t>
+          <t>293586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>417071</t>
+          <t>438922</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>385583</t>
+          <t>405821</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>452174</t>
+          <t>472638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>739735</t>
+          <t>775751</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>739735</t>
+          <t>775751</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>739735</t>
+          <t>775751</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>881842</t>
+          <t>947748</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>881842</t>
+          <t>947748</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>881842</t>
+          <t>947748</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1621577</t>
+          <t>1723499</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1621577</t>
+          <t>1723499</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1621577</t>
+          <t>1723499</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>224789</t>
+          <t>250298</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193576</t>
+          <t>217490</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>261070</t>
+          <t>287101</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>259275</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>195011</t>
+          <t>233578</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>273208</t>
+          <t>289721</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465627</t>
+          <t>509573</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>406690</t>
+          <t>466343</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>513642</t>
+          <t>554469</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>676685</t>
+          <t>737938</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>625343</t>
+          <t>689036</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>726421</t>
+          <t>794274</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>863993</t>
+          <t>729878</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>690072</t>
+          <t>687129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1289495</t>
+          <t>773954</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1540678</t>
+          <t>1467815</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1361363</t>
+          <t>1399944</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2064760</t>
+          <t>1540700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>757461</t>
+          <t>812251</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>708663</t>
+          <t>763814</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>815224</t>
+          <t>865207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>842119</t>
+          <t>899285</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>685357</t>
+          <t>853872</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>935607</t>
+          <t>944993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1599579</t>
+          <t>1711535</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1414719</t>
+          <t>1640220</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1695985</t>
+          <t>1773142</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>453345</t>
+          <t>494140</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>415050</t>
+          <t>452116</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>493998</t>
+          <t>539448</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>500960</t>
+          <t>553910</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>404168</t>
+          <t>519324</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>552432</t>
+          <t>591290</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>954305</t>
+          <t>1048050</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>842092</t>
+          <t>995693</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1012934</t>
+          <t>1105942</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>547134</t>
+          <t>595185</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>507085</t>
+          <t>556945</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>591547</t>
+          <t>643699</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>756327</t>
+          <t>834696</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>613698</t>
+          <t>792308</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>826403</t>
+          <t>882383</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1303460</t>
+          <t>1429881</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1158827</t>
+          <t>1372169</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1380547</t>
+          <t>1500380</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2659413</t>
+          <t>2889811</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2659413</t>
+          <t>2889811</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2659413</t>
+          <t>2889811</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3204237</t>
+          <t>3277044</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3204237</t>
+          <t>3277044</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3204237</t>
+          <t>3277044</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5863650</t>
+          <t>6166855</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5863650</t>
+          <t>6166855</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5863650</t>
+          <t>6166855</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
